--- a/data/trans_camb/POLIPATOLOGIA_2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_2-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 14,33</t>
+          <t>5,66; 14,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,06</t>
+          <t>1,11; 10,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,9; 21,9</t>
+          <t>11,68; 21,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,11</t>
+          <t>4,52; 12,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 12,17</t>
+          <t>3,93; 12,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,27; 20,98</t>
+          <t>13,42; 20,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,07</t>
+          <t>6,52; 12,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,26</t>
+          <t>4,0; 10,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,29; 20,64</t>
+          <t>14,48; 20,68</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,05; 39,6</t>
+          <t>13,66; 39,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 27,06</t>
+          <t>2,74; 28,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,09; 59,43</t>
+          <t>28,52; 59,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 22,68</t>
+          <t>7,8; 22,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 22,48</t>
+          <t>6,92; 22,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,16; 39,27</t>
+          <t>23,21; 38,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,82; 25,9</t>
+          <t>13,18; 27,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 22,31</t>
+          <t>8,07; 21,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,83; 44,37</t>
+          <t>29,14; 44,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,88</t>
+          <t>2,23; 6,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,3</t>
+          <t>4,59; 9,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 18,73</t>
+          <t>6,87; 18,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,76</t>
+          <t>1,89; 7,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 10,34</t>
+          <t>4,27; 9,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,1; 40,36</t>
+          <t>19,6; 42,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,51</t>
+          <t>2,68; 6,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,97</t>
+          <t>5,17; 8,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 30,46</t>
+          <t>14,64; 29,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 70,89</t>
+          <t>17,41; 66,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,54; 94,07</t>
+          <t>37,34; 95,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,41; 181,62</t>
+          <t>63,23; 179,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 42,96</t>
+          <t>8,77; 41,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,86; 56,48</t>
+          <t>19,98; 51,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,36; 213,46</t>
+          <t>95,71; 223,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 45,35</t>
+          <t>16,86; 45,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,07; 61,96</t>
+          <t>31,94; 61,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,62; 201,46</t>
+          <t>93,3; 192,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 4,18</t>
+          <t>-4,05; 4,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 11,64</t>
+          <t>2,31; 11,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,41; 19,85</t>
+          <t>11,49; 20,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 6,44</t>
+          <t>-3,37; 7,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,51</t>
+          <t>-3,48; 6,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,55; 23,66</t>
+          <t>13,78; 23,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,88</t>
+          <t>-2,61; 4,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,47</t>
+          <t>1,0; 8,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,16; 20,75</t>
+          <t>14,31; 20,96</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,9; 43,28</t>
+          <t>-31,47; 48,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,02; 126,08</t>
+          <t>13,5; 123,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,71; 215,37</t>
+          <t>85,47; 225,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 40,77</t>
+          <t>-15,98; 45,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 41,25</t>
+          <t>-16,95; 41,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62,32; 152,19</t>
+          <t>63,68; 150,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 28,35</t>
+          <t>-15,3; 32,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 57,33</t>
+          <t>5,77; 60,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,08; 161,81</t>
+          <t>85,83; 164,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,83</t>
+          <t>2,56; 6,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,13</t>
+          <t>2,16; 6,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 13,75</t>
+          <t>3,45; 13,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,46</t>
+          <t>2,77; 7,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,04</t>
+          <t>0,4; 5,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 26,03</t>
+          <t>12,39; 25,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,58</t>
+          <t>3,23; 6,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,93</t>
+          <t>1,79; 4,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 18,92</t>
+          <t>9,38; 18,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,99; 36,55</t>
+          <t>12,23; 35,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,97; 32,61</t>
+          <t>10,25; 32,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,45; 71,32</t>
+          <t>18,76; 71,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,21; 23,06</t>
+          <t>7,99; 23,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 15,44</t>
+          <t>1,14; 16,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,36; 77,51</t>
+          <t>35,8; 77,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,65; 25,26</t>
+          <t>11,65; 24,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,97; 18,91</t>
+          <t>6,5; 19,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35,26; 70,97</t>
+          <t>34,81; 71,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_2-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,0</t>
+          <t>13,99</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,98</t>
+          <t>16,42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,56</t>
+          <t>15,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 14,55</t>
+          <t>5,34; 14,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,33</t>
+          <t>0,16; 9,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,68; 21,99</t>
+          <t>9,12; 19,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 12,05</t>
+          <t>4,08; 11,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 12,18</t>
+          <t>4,44; 12,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,42; 20,7</t>
+          <t>12,81; 20,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 12,57</t>
+          <t>6,19; 11,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,25</t>
+          <t>3,22; 10,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,48; 20,68</t>
+          <t>12,39; 18,6</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,66; 39,87</t>
+          <t>12,95; 39,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 28,36</t>
+          <t>0,35; 27,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,52; 59,93</t>
+          <t>22,05; 53,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 22,46</t>
+          <t>7,14; 22,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 22,82</t>
+          <t>7,84; 23,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,21; 38,6</t>
+          <t>22,31; 38,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 27,23</t>
+          <t>12,56; 25,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 21,68</t>
+          <t>6,4; 21,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,14; 44,53</t>
+          <t>24,66; 39,73</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,73</t>
+          <t>17,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,41</t>
+          <t>19,49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20,59</t>
+          <t>18,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,68</t>
+          <t>2,26; 6,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 9,27</t>
+          <t>4,74; 9,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 18,6</t>
+          <t>14,73; 19,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,84</t>
+          <t>1,96; 7,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,63</t>
+          <t>4,01; 9,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,6; 42,24</t>
+          <t>16,5; 22,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,55</t>
+          <t>2,72; 6,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 8,84</t>
+          <t>5,29; 8,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,64; 29,08</t>
+          <t>16,77; 20,59</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134,49%</t>
+          <t>159,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>133,07%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>134,99%</t>
+          <t>121,55%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,41; 66,41</t>
+          <t>18,38; 66,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,34; 95,45</t>
+          <t>39,71; 94,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,23; 179,75</t>
+          <t>121,68; 203,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 41,54</t>
+          <t>9,02; 41,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,98; 51,98</t>
+          <t>18,88; 53,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,71; 223,36</t>
+          <t>76,43; 120,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,86; 45,9</t>
+          <t>16,91; 43,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,94; 61,67</t>
+          <t>33,06; 62,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,3; 192,69</t>
+          <t>102,69; 143,54</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,83</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>18,85</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,59</t>
+          <t>17,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 4,32</t>
+          <t>-4,54; 3,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 11,53</t>
+          <t>1,85; 11,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,49; 20,37</t>
+          <t>11,64; 20,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 7,59</t>
+          <t>-3,98; 6,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 6,71</t>
+          <t>-3,77; 6,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,78; 23,47</t>
+          <t>14,18; 23,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,12</t>
+          <t>-2,49; 4,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,0</t>
+          <t>1,11; 7,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,31; 20,96</t>
+          <t>14,71; 21,43</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141,12%</t>
+          <t>146,19%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>100,81%</t>
+          <t>101,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>120,33%</t>
+          <t>122,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 48,31</t>
+          <t>-33,85; 41,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,5; 123,49</t>
+          <t>13,28; 117,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,47; 225,82</t>
+          <t>86,81; 224,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 45,97</t>
+          <t>-18,93; 41,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 41,4</t>
+          <t>-18,31; 41,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,68; 150,88</t>
+          <t>64,69; 149,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 32,04</t>
+          <t>-15,36; 32,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,77; 60,03</t>
+          <t>6,73; 60,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85,83; 164,24</t>
+          <t>87,4; 163,12</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,66</t>
+          <t>12,48</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,52</t>
+          <t>12,61</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,76</t>
+          <t>12,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,57</t>
+          <t>2,41; 6,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,03</t>
+          <t>2,15; 6,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 13,73</t>
+          <t>9,86; 14,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,5</t>
+          <t>2,79; 7,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,21</t>
+          <t>0,29; 4,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 25,64</t>
+          <t>10,29; 14,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,36</t>
+          <t>3,31; 6,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,93</t>
+          <t>1,89; 4,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,38; 18,97</t>
+          <t>11,07; 14,15</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,23; 35,16</t>
+          <t>11,62; 35,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,25; 32,04</t>
+          <t>10,17; 32,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,76; 71,91</t>
+          <t>46,55; 76,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,99; 23,23</t>
+          <t>8,13; 23,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 16,13</t>
+          <t>0,83; 15,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,8; 77,45</t>
+          <t>29,7; 45,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,65; 24,53</t>
+          <t>12,01; 24,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,5; 19,32</t>
+          <t>6,69; 18,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,81; 71,76</t>
+          <t>40,08; 54,57</t>
         </is>
       </c>
     </row>
